--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59014,7 +59014,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59121,14 +59121,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 56329-2023</t>
+          <t>A 54972-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -59178,14 +59178,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 54972-2023</t>
+          <t>A 56329-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -59235,14 +59235,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 56347-2023</t>
+          <t>A 56325-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -59292,14 +59292,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 56325-2023</t>
+          <t>A 56339-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -59349,14 +59349,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 56339-2023</t>
+          <t>A 56347-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59520,14 +59520,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 55805-2023</t>
+          <t>A 55849-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -59577,14 +59577,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 55849-2023</t>
+          <t>A 56859-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -59641,7 +59641,7 @@
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59691,14 +59691,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 56863-2023</t>
+          <t>A 55805-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -59748,14 +59748,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56859-2023</t>
+          <t>A 56863-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59919,14 +59919,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 57589-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -59976,14 +59976,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 57603-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 57593-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57583-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57589-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60204,14 +60204,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57593-2023</t>
+          <t>A 57603-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60261,14 +60261,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57583-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60325,7 +60325,7 @@
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60375,14 +60375,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 58131-2023</t>
+          <t>A 57386-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -60432,14 +60432,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 57386-2023</t>
+          <t>A 57972-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60489,14 +60489,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 57972-2023</t>
+          <t>A 58131-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1017"/>
+  <dimension ref="A1:Y1018"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58888,14 +58888,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 54188-2023</t>
+          <t>A 54320-2023</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -58945,14 +58945,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 54318-2023</t>
+          <t>A 54188-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58964,13 +58964,8 @@
           <t>KRAMFORS</t>
         </is>
       </c>
-      <c r="F986" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G986" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -59007,14 +59002,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 54320-2023</t>
+          <t>A 54318-2023</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59026,8 +59021,13 @@
           <t>KRAMFORS</t>
         </is>
       </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G987" t="n">
-        <v>12.9</v>
+        <v>6.8</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59577,14 +59577,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 56859-2023</t>
+          <t>A 55805-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -59641,7 +59641,7 @@
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59691,14 +59691,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 55805-2023</t>
+          <t>A 56863-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -59748,14 +59748,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56863-2023</t>
+          <t>A 56859-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59919,14 +59919,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57583-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -59976,14 +59976,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57593-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 57593-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57589-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60204,14 +60204,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57603-2023</t>
+          <t>A 57589-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60261,14 +60261,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57583-2023</t>
+          <t>A 57603-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60318,14 +60318,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 57146-2023</t>
+          <t>A 57386-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -60375,14 +60375,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 57386-2023</t>
+          <t>A 57972-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -60432,14 +60432,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 57972-2023</t>
+          <t>A 58131-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60489,14 +60489,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 58131-2023</t>
+          <t>A 57146-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
       </c>
       <c r="R1016" s="2" t="inlineStr"/>
     </row>
-    <row r="1017">
+    <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
           <t>A 59113-2023</t>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60775,6 +60775,63 @@
         <v>0</v>
       </c>
       <c r="R1017" s="2" t="inlineStr"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>A 60566-2023</t>
+        </is>
+      </c>
+      <c r="B1018" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="C1018" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1018" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1018" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1018"/>
+  <dimension ref="A1:Y1019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58888,14 +58888,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 54320-2023</t>
+          <t>A 54188-2023</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -58945,14 +58945,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 54188-2023</t>
+          <t>A 54320-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58965,7 +58965,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -59009,7 +59009,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59520,14 +59520,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 55849-2023</t>
+          <t>A 55805-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -59577,14 +59577,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 55805-2023</t>
+          <t>A 56863-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -59641,7 +59641,7 @@
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59691,14 +59691,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 56863-2023</t>
+          <t>A 55849-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -59755,7 +59755,7 @@
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59862,14 +59862,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 56401-2023</t>
+          <t>A 57583-2023</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>16.4</v>
+        <v>2.9</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59919,14 +59919,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 57583-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -59976,14 +59976,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 56401-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>0.9</v>
+        <v>16.4</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57593-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57593-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60211,7 +60211,7 @@
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60318,14 +60318,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 57386-2023</t>
+          <t>A 57146-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -60375,14 +60375,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 57972-2023</t>
+          <t>A 57386-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -60432,14 +60432,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 58131-2023</t>
+          <t>A 57972-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>7.7</v>
+        <v>4.4</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60489,14 +60489,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 57146-2023</t>
+          <t>A 58131-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
       </c>
       <c r="R1017" s="2" t="inlineStr"/>
     </row>
-    <row r="1018">
+    <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
           <t>A 60566-2023</t>
@@ -60786,7 +60786,7 @@
         <v>45259</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60832,6 +60832,63 @@
         <v>0</v>
       </c>
       <c r="R1018" s="2" t="inlineStr"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>A 60851-2023</t>
+        </is>
+      </c>
+      <c r="B1019" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C1019" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1019" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1019" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58888,14 +58888,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 54188-2023</t>
+          <t>A 54320-2023</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -58945,14 +58945,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 54320-2023</t>
+          <t>A 54188-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58965,7 +58965,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>12.9</v>
+        <v>0.9</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -59009,7 +59009,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59121,14 +59121,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 54972-2023</t>
+          <t>A 56347-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -59178,14 +59178,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 56329-2023</t>
+          <t>A 54972-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -59242,7 +59242,7 @@
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59349,14 +59349,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 56347-2023</t>
+          <t>A 56329-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59520,14 +59520,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 55805-2023</t>
+          <t>A 55849-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -59577,14 +59577,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 56863-2023</t>
+          <t>A 56866-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -59634,14 +59634,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 56866-2023</t>
+          <t>A 56859-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -59691,14 +59691,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 55849-2023</t>
+          <t>A 55805-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -59748,14 +59748,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56859-2023</t>
+          <t>A 56863-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59862,14 +59862,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 57583-2023</t>
+          <t>A 56401-2023</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>2.9</v>
+        <v>16.4</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59919,14 +59919,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 57589-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -59976,14 +59976,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 56401-2023</t>
+          <t>A 57603-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>16.4</v>
+        <v>5.2</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57593-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57593-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60204,14 +60204,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57589-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60261,14 +60261,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57603-2023</t>
+          <t>A 57583-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60318,14 +60318,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 57146-2023</t>
+          <t>A 58131-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -60382,7 +60382,7 @@
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60432,14 +60432,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 57972-2023</t>
+          <t>A 57146-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60489,14 +60489,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 58131-2023</t>
+          <t>A 57972-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>7.7</v>
+        <v>4.4</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45259</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45260</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1019"/>
+  <dimension ref="A1:Y1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59121,14 +59121,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 56347-2023</t>
+          <t>A 54972-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -59178,14 +59178,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 54972-2023</t>
+          <t>A 56329-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -59235,14 +59235,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 56325-2023</t>
+          <t>A 56347-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -59292,14 +59292,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 56339-2023</t>
+          <t>A 56325-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -59349,14 +59349,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 56329-2023</t>
+          <t>A 56339-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59577,14 +59577,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 56866-2023</t>
+          <t>A 55805-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -59634,14 +59634,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 56859-2023</t>
+          <t>A 56863-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -59691,14 +59691,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 55805-2023</t>
+          <t>A 56866-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -59748,14 +59748,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56863-2023</t>
+          <t>A 56859-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59919,14 +59919,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 57589-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -59976,14 +59976,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 57603-2023</t>
+          <t>A 57589-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57603-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57593-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57593-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60204,14 +60204,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60268,7 +60268,7 @@
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60318,14 +60318,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 58131-2023</t>
+          <t>A 57146-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -60382,7 +60382,7 @@
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60432,14 +60432,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 57146-2023</t>
+          <t>A 57972-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60489,14 +60489,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 57972-2023</t>
+          <t>A 58131-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45259</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
       </c>
       <c r="R1018" s="2" t="inlineStr"/>
     </row>
-    <row r="1019">
+    <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
           <t>A 60851-2023</t>
@@ -60843,7 +60843,7 @@
         <v>45260</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60889,6 +60889,177 @@
         <v>0</v>
       </c>
       <c r="R1019" s="2" t="inlineStr"/>
+    </row>
+    <row r="1020" ht="15" customHeight="1">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>A 61172-2023</t>
+        </is>
+      </c>
+      <c r="B1020" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="C1020" s="1" t="n">
+        <v>45263</v>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1020" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1020" s="2" t="inlineStr"/>
+    </row>
+    <row r="1021" ht="15" customHeight="1">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>A 61173-2023</t>
+        </is>
+      </c>
+      <c r="B1021" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="C1021" s="1" t="n">
+        <v>45263</v>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1021" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1021" s="2" t="inlineStr"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>A 61174-2023</t>
+        </is>
+      </c>
+      <c r="B1022" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="C1022" s="1" t="n">
+        <v>45263</v>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1022" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1022" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59121,14 +59121,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 54972-2023</t>
+          <t>A 56329-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -59178,14 +59178,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 56329-2023</t>
+          <t>A 56347-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59235,14 +59235,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 56347-2023</t>
+          <t>A 56325-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -59292,14 +59292,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 56325-2023</t>
+          <t>A 56339-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -59349,14 +59349,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 56339-2023</t>
+          <t>A 54972-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59641,7 +59641,7 @@
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59698,7 +59698,7 @@
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59919,14 +59919,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 57589-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -59976,14 +59976,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 57589-2023</t>
+          <t>A 57583-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57603-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57603-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57593-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60204,14 +60204,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57593-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60261,14 +60261,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57583-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60325,7 +60325,7 @@
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60382,7 +60382,7 @@
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45259</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45260</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60900,7 +60900,7 @@
         <v>45262</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60950,14 +60950,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 61173-2023</t>
+          <t>A 61174-2023</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60970,7 +60970,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -61007,14 +61007,14 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 61174-2023</t>
+          <t>A 61173-2023</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61027,7 +61027,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1022"/>
+  <dimension ref="A1:Y1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59121,14 +59121,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 56329-2023</t>
+          <t>A 56347-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59178,14 +59178,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 56347-2023</t>
+          <t>A 54972-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -59242,7 +59242,7 @@
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59349,14 +59349,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 54972-2023</t>
+          <t>A 56329-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59577,14 +59577,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 55805-2023</t>
+          <t>A 56866-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -59634,14 +59634,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 56863-2023</t>
+          <t>A 56859-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -59691,14 +59691,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 56866-2023</t>
+          <t>A 55805-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -59748,14 +59748,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56859-2023</t>
+          <t>A 56863-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59919,14 +59919,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 57589-2023</t>
+          <t>A 57583-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -59976,14 +59976,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 57583-2023</t>
+          <t>A 57589-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57603-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57603-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60211,7 +60211,7 @@
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60261,14 +60261,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60318,14 +60318,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 57146-2023</t>
+          <t>A 57386-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -60375,14 +60375,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 57386-2023</t>
+          <t>A 57972-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -60432,14 +60432,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 57972-2023</t>
+          <t>A 58131-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60489,14 +60489,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 58131-2023</t>
+          <t>A 57146-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45259</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45260</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60900,7 +60900,7 @@
         <v>45262</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45262</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61004,7 +61004,7 @@
       </c>
       <c r="R1021" s="2" t="inlineStr"/>
     </row>
-    <row r="1022">
+    <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
           <t>A 61173-2023</t>
@@ -61014,7 +61014,7 @@
         <v>45262</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61060,6 +61060,177 @@
         <v>0</v>
       </c>
       <c r="R1022" s="2" t="inlineStr"/>
+    </row>
+    <row r="1023" ht="15" customHeight="1">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>A 61466-2023</t>
+        </is>
+      </c>
+      <c r="B1023" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C1023" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1023" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1023" s="2" t="inlineStr"/>
+    </row>
+    <row r="1024" ht="15" customHeight="1">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>A 61467-2023</t>
+        </is>
+      </c>
+      <c r="B1024" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C1024" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1024" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1024" s="2" t="inlineStr"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>A 61468-2023</t>
+        </is>
+      </c>
+      <c r="B1025" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C1025" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1025" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1025" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1025"/>
+  <dimension ref="A1:Y1026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59121,14 +59121,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 56347-2023</t>
+          <t>A 54972-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -59178,14 +59178,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 54972-2023</t>
+          <t>A 56347-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -59235,14 +59235,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 56325-2023</t>
+          <t>A 56329-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -59292,14 +59292,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 56339-2023</t>
+          <t>A 56325-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -59349,14 +59349,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 56329-2023</t>
+          <t>A 56339-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59520,14 +59520,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 55849-2023</t>
+          <t>A 55805-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -59584,7 +59584,7 @@
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59634,14 +59634,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 56859-2023</t>
+          <t>A 56863-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -59691,14 +59691,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 55805-2023</t>
+          <t>A 55849-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -59748,14 +59748,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56863-2023</t>
+          <t>A 56859-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59919,14 +59919,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 57583-2023</t>
+          <t>A 57589-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -59976,14 +59976,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 57589-2023</t>
+          <t>A 57603-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57603-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57593-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60204,14 +60204,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57593-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60261,14 +60261,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 57583-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60325,7 +60325,7 @@
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60382,7 +60382,7 @@
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60432,14 +60432,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 58131-2023</t>
+          <t>A 57146-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60489,14 +60489,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 57146-2023</t>
+          <t>A 58131-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45259</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45260</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60893,14 +60893,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 61172-2023</t>
+          <t>A 61619-2023</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
-        <v>45262</v>
+        <v>45261</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60913,7 +60913,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -60957,7 +60957,7 @@
         <v>45262</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61007,14 +61007,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 61173-2023</t>
+          <t>A 61172-2023</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61027,7 +61027,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -61064,14 +61064,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 61466-2023</t>
+          <t>A 61173-2023</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
-        <v>45264</v>
+        <v>45262</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61084,7 +61084,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -61128,7 +61128,7 @@
         <v>45264</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61175,17 +61175,17 @@
       </c>
       <c r="R1024" s="2" t="inlineStr"/>
     </row>
-    <row r="1025">
+    <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 61468-2023</t>
+          <t>A 61466-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61198,39 +61198,96 @@
         </is>
       </c>
       <c r="G1025" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1025" s="2" t="inlineStr"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>A 61468-2023</t>
+        </is>
+      </c>
+      <c r="B1026" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C1026" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1026" t="n">
         <v>0.8</v>
       </c>
-      <c r="H1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1025" s="2" t="inlineStr"/>
+      <c r="H1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1026" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1026"/>
+  <dimension ref="A1:Y1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>44938</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>44939</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44942</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>44942</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44943</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>44945</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44946</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44946</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>44946</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44949</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44949</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>44951</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>44956</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>44956</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44956</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>44956</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44956</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44958</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44958</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44958</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>44958</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>44958</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44958</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44959</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>44964</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44965</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44965</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44965</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>44965</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44967</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44971</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44978</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>44980</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44984</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>44984</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44988</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>44991</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>44998</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44999</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>44999</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45000</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45000</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45000</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45000</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45008</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45008</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45014</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45015</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45028</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45033</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45033</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45033</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45033</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45034</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45034</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45034</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45034</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45034</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45034</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45034</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45035</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45035</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45036</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45036</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45036</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>45036</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45036</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45036</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45036</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45040</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45043</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45043</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45044</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45044</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45049</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45049</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45049</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45049</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45051</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45051</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45055</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45056</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45057</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45058</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45062</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45062</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45065</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45065</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45068</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45068</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45071</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45084</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45084</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45085</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45089</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45090</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45092</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45092</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45096</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45096</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45096</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45099</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45099</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45099</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45099</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>45110</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45110</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45111</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45111</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51229,7 +51229,7 @@
         <v>45111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45113</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45113</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45114</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45116</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45121</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45124</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45124</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45127</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45127</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45134</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45135</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45139</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45139</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45139</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45143</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45146</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45146</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45146</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45148</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45153</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45153</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45153</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45154</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45155</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45156</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45159</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45159</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45161</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45162</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45163</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45167</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45168</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45168</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45169</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45169</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45169</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45169</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45169</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45173</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45173</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45173</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45173</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45173</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45180</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45182</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45182</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45182</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45182</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45183</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45183</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45189</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45189</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45189</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45190</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45190</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45190</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45191</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45191</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45190</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45190</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45191</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45192</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45192</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45191</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45192</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45191</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>45191</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45195</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45197</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45197</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45198</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45199</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45201</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45202</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45202</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>45203</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45203</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45205</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45204</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45205</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45205</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45205</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45205</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45205</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45206</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45208</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45209</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45210</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45210</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45211</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45211</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45212</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45213</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45215</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45216</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>45216</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45216</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45216</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45217</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45217</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45219</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45219</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45219</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45223</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45223</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45224</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45225</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45225</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45225</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>45225</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45225</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45230</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45231</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45232</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>45232</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>45232</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>45233</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         <v>45236</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         <v>45236</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>45236</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>45236</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>45236</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45237</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45237</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         <v>45239</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         <v>45239</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59634,14 +59634,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 56863-2023</t>
+          <t>A 55849-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -59691,14 +59691,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 55849-2023</t>
+          <t>A 56859-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -59748,14 +59748,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 56859-2023</t>
+          <t>A 56863-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -59812,7 +59812,7 @@
         <v>45240</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45243</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59926,7 +59926,7 @@
         <v>45243</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45243</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60033,14 +60033,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 57564-2023</t>
+          <t>A 57583-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -60090,14 +60090,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 57593-2023</t>
+          <t>A 57672-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -60147,14 +60147,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 57672-2023</t>
+          <t>A 57564-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -60204,14 +60204,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 57600-2023</t>
+          <t>A 57593-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60261,14 +60261,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 57583-2023</t>
+          <t>A 57600-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60318,14 +60318,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 57386-2023</t>
+          <t>A 57146-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -60375,14 +60375,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 57972-2023</t>
+          <t>A 57386-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -60432,14 +60432,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 57146-2023</t>
+          <t>A 57972-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60496,7 +60496,7 @@
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45247</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45250</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45251</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45253</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45259</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45260</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60900,7 +60900,7 @@
         <v>45261</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45262</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61007,14 +61007,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 61172-2023</t>
+          <t>A 61173-2023</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61027,7 +61027,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -61064,14 +61064,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 61173-2023</t>
+          <t>A 61172-2023</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61084,7 +61084,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -61121,14 +61121,14 @@
     <row r="1024" ht="15" customHeight="1">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>A 61467-2023</t>
+          <t>A 61466-2023</t>
         </is>
       </c>
       <c r="B1024" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61141,7 +61141,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -61178,14 +61178,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 61466-2023</t>
+          <t>A 61467-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61198,7 +61198,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -61232,7 +61232,7 @@
       </c>
       <c r="R1025" s="2" t="inlineStr"/>
     </row>
-    <row r="1026">
+    <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
           <t>A 61468-2023</t>
@@ -61242,7 +61242,7 @@
         <v>45264</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61288,6 +61288,177 @@
         <v>0</v>
       </c>
       <c r="R1026" s="2" t="inlineStr"/>
+    </row>
+    <row r="1027" ht="15" customHeight="1">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>A 61914-2023</t>
+        </is>
+      </c>
+      <c r="B1027" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C1027" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1027" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1027" s="2" t="inlineStr"/>
+    </row>
+    <row r="1028" ht="15" customHeight="1">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>A 61877-2023</t>
+        </is>
+      </c>
+      <c r="B1028" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C1028" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1028" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1028" s="2" t="inlineStr"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>A 61909-2023</t>
+        </is>
+      </c>
+      <c r="B1029" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C1029" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>VÄSTERNORRLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>KRAMFORS</t>
+        </is>
+      </c>
+      <c r="G1029" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1029" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1029"/>
+  <dimension ref="A1:Y1030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43816</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>44287</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44364</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44364</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>44810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>43803</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>43852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>43801</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>43916</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>43413</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>44411</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44440</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45211</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>43357</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45204</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>43423</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>43788</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>43886</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>43780</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>43924</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>44173</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44315</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>43901</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45161</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43329</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>43482</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>43853</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>43922</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44215</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44377</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44524</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>43546</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>43707</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>43853</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44299</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44726</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45114</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45114</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45161</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45182</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45195</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>43920</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45065</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45105</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45195</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45204</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45238</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45244</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43318</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43318</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43318</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>43325</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43325</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>43329</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>43332</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>43340</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>43355</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43355</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>43355</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>43355</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>43364</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>43364</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>43364</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>43367</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43374</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43388</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43391</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43391</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43392</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>43395</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43395</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43396</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>43405</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>43412</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>43416</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>43420</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>43424</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>43424</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>43427</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>43430</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43432</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43433</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>43433</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>43433</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>43437</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>43437</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>43467</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>43468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>43480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>43481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>43493</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>43494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>43494</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43518</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>43524</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>43525</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>43535</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>43543</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43543</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>43543</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43543</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>43550</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>43550</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>43551</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>43551</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>43563</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>43564</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>43564</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>43567</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>43578</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>43584</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>43584</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>43584</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43584</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>43585</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>43585</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>43591</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>43593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>43605</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43609</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43612</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>43620</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>43620</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>43620</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>43626</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>43626</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>43626</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43647</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43657</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43683</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43696</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>43696</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43724</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43727</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43728</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>43732</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>43734</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>43740</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>43739</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>43739</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>43739</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43747</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43762</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43763</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43766</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43768</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>43773</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>43773</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43774</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43774</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43774</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>43787</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>43789</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>43803</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>43810</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>43812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>43812</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43819</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43819</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43845</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43846</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43850</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>43852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>43852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>43861</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>43867</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>43868</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>43874</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43875</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>43875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>43875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>43875</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>43881</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>43881</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>43892</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>43899</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>43899</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>43909</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>43916</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>43936</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>43937</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>43950</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>43957</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>43963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>43964</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>43964</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>43969</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>43977</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>43977</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>43979</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43983</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>43990</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43992</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>43994</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43998</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44001</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44004</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44005</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44005</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44005</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44012</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44012</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44014</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44018</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44018</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44019</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44019</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44027</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44028</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44043</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44043</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44046</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44047</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44054</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44054</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44057</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44057</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44057</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44060</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44071</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44088</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44090</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44089</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44090</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44091</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44095</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44096</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44109</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44109</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44109</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44109</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44109</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44119</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44119</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44125</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44132</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44132</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44137</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44147</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44147</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44154</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44154</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44154</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>44154</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44155</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44160</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44161</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44167</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44167</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44167</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44172</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44173</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44174</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44175</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44179</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>44181</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44181</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44181</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44181</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44186</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44193</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44201</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44201</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44207</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44207</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44207</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44207</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44210</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44211</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44215</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44216</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44221</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44224</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44228</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44228</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44229</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44235</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>44237</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44239</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44243</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44243</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44244</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44245</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44246</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44252</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44256</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44264</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44267</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44267</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44272</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44278</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44280</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44284</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44287</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44292</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44292</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44292</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44293</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44293</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44294</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44294</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44298</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44302</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44303</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44303</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44302</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44302</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44307</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44308</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44308</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44308</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44308</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44309</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44310</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44309</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44310</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44310</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44310</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44314</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44316</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44315</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44316</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44315</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44316</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44316</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44316</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44319</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44319</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>44320</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44321</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44323</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>44328</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44334</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44336</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44341</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44343</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44343</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44343</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44344</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44347</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44349</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44349</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44349</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44349</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44355</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44356</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44356</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44356</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44363</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44362</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44369</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44370</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44375</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44377</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44378</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>44379</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44379</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44384</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44387</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44388</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44388</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44390</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>44424</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44424</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44424</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44426</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44428</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>44428</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44428</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44432</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>44433</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>44434</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44438</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44440</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44447</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44452</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44456</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44456</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44459</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>44460</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44462</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44465</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44466</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44467</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44469</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>44474</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44475</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44475</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44476</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44477</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44483</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44484</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44484</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44484</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44484</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44495</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44496</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44503</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44503</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44503</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44503</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44503</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>44504</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44508</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>44508</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44508</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44508</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44509</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>44509</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44509</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44509</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>44511</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44511</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44515</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44516</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44516</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44517</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44518</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44523</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44523</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44523</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44525</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44529</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44529</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44529</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>44529</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44536</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44540</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44540</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44546</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>44546</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>44546</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>44550</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44564</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44566</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>44571</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44572</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44573</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44573</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>44574</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44574</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44574</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44578</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44581</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44581</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>44581</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44581</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44581</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44584</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44587</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44592</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44592</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>44594</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44594</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44594</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44594</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44606</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44607</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44608</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44608</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44610</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44613</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44616</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44628</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44629</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>44629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44629</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44629</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44629</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>44629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44634</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44634</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44635</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>44638</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44638</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44644</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>44645</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44659</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44687</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44688</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44698</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44701</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44700</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44708</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44712</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44712</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44713</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44715</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44720</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44719</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44722</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44726</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44726</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44727</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44739</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44742</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44744</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44747</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44749</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44749</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44750</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44761</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44762</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44769</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44774</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44774</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44775</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44775</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44782</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44782</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44782</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44784</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44788</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44792</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44792</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44792</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44793</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44795</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44798</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44802</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44802</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44802</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44803</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>44803</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44804</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44804</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44803</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44804</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44804</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44804</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44804</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44804</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44811</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44812</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44812</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44813</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>44813</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>44817</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44818</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44817</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44819</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44819</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44823</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44823</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>44824</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44826</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44826</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44830</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44833</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>44833</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44834</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>44835</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44837</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44837</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44840</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44847</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>44854</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44856</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44859</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44859</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44859</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>44860</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>44861</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44861</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44865</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44866</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44868</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44868</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44868</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44869</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44869</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44872</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44872</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>44872</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44873</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44874</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44874</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44874</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44876</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44876</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>44879</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44880</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>44880</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>44880</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>44883</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44883</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>44883</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44888</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>44888</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>44894</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>44894</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44894</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44896</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44897</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44901</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44903</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44904</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>44904</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>44904</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44907</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44907</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44908</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44908</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>44908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44908</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44916</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>44916</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44938</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ 